--- a/public/templates/planilla.xlsx
+++ b/public/templates/planilla.xlsx
@@ -479,14 +479,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD95988"/>
-        <bgColor rgb="FFD95988"/>
+        <fgColor rgb="FFFF6A2B"/>
+        <bgColor rgb="FFFF6A2B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9C1944"/>
-        <bgColor rgb="FF9C1944"/>
+        <fgColor rgb="FFC2410C"/>
+        <bgColor rgb="FFC2410C"/>
       </patternFill>
     </fill>
     <fill>
@@ -879,8 +879,8 @@
       <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFE0EA"/>
-          <bgColor rgb="FFFFE0EA"/>
+          <fgColor rgb="FFFFEBDD"/>
+          <bgColor rgb="FFFFEBDD"/>
         </patternFill>
       </fill>
       <border/>
